--- a/tests/testcase.xlsx
+++ b/tests/testcase.xlsx
@@ -5,18 +5,24 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\Nam3\CNPM\FinalProject\lan-may-cafe\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8395C39A-B28A-460E-BCC6-D5C845873C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAC1910-9F4F-4D2C-9933-D4C518652015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7CD00C44-CE7E-4ADA-99E2-520E40CF5D28}"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Case" sheetId="2" r:id="rId1"/>
+    <sheet name="Test Plan" sheetId="3" r:id="rId1"/>
+    <sheet name="Test Case" sheetId="2" r:id="rId2"/>
+    <sheet name="Tổng hợp" sheetId="4" r:id="rId3"/>
+    <sheet name="Bug Report" sheetId="5" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Case'!$A$1:$O$47</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="478">
   <si>
     <t>Tên nút theo giao diện của Hậu, cập nhật khi nhận bản 07/10 [X14].</t>
   </si>
@@ -1239,12 +1245,345 @@
   <si>
     <t>ID</t>
   </si>
+  <si>
+    <t>Critical và High: dev sửa trong ngày nhận (Tuấn T8, An A8, Hậu H5). Medium/Low chưa kịp sửa thì chuyển Duy đưa vào mục "Hướng phát triển".</t>
+  </si>
+  <si>
+    <t>Hạn sửa bug</t>
+  </si>
+  <si>
+    <t>Critical: sai tiền, thu trùng, mất hoặc hỏng dữ liệu. High: ảnh hưởng trực tiếp nghiệp vụ hoặc thiếu xử lý alternative flow (ví dụ gọi được món đã hết). Medium: sai thông báo hoặc mã lỗi nhưng nghiệp vụ vẫn đúng. Low: lỗi giao diện, chính tả.</t>
+  </si>
+  <si>
+    <t>Mức độ nghiêm trọng bug</t>
+  </si>
+  <si>
+    <t>Cao: luồng chính, biên, alternative flow quan trọng. Trung: negative/alternative còn lại. Thấp: ít ảnh hưởng nghiệp vụ.</t>
+  </si>
+  <si>
+    <t>Ưu tiên chạy</t>
+  </si>
+  <si>
+    <t>TC-[số UC]-[số thứ tự], ví dụ TC-01-03. Bug: BUG-N5-[số], ví dụ BUG-N5-001. Số UC theo UC diagram cuối (UC01–UC25).</t>
+  </si>
+  <si>
+    <t>Mã test case / bug</t>
+  </si>
+  <si>
+    <t>Quy ước</t>
+  </si>
+  <si>
+    <t>TC thanh toán (UC10), sửa/hủy món (UC04) làm thay đổi dữ liệu: mỗi TC cần đơn còn nguyên, nên chạy reset_db giữa các TC hoặc tạo đơn mới bằng UC01. TC-21-07 khóa tài khoản [TK_PV] nên reset_db sau đó. Nếu thiếu thời gian, chạy các TC ưu tiên "Cao" trước.</t>
+  </si>
+  <si>
+    <t>Lưu ý khi chạy</t>
+  </si>
+  <si>
+    <t>Mỗi TC FAIL viết 1 bug ở sheet "Bug Report" với đủ 7 trường C6-D2; gửi Tuấn, An, Hậu trong ngày 08/10.</t>
+  </si>
+  <si>
+    <t>Bước 3 – Bug report</t>
+  </si>
+  <si>
+    <t>Làm đúng từng bước, không bỏ bước. Ghi Actual Result đúng như quan sát được, không ghi điều bạn nghĩ sẽ xảy ra. Khớp Expected hoàn toàn: PASS; khác ở bất kỳ điểm nào: FAIL. Chụp ảnh bằng chứng, ghi tên file vào cột "Ảnh bằng chứng".</t>
+  </si>
+  <si>
+    <t>Bước 2 – Chạy từng TC</t>
+  </si>
+  <si>
+    <t>Chạy reset_db (script của An) để đưa CSDL về trạng thái ban đầu trước mỗi nhóm test. Ghi lại phiên bản ứng dụng và CSDL ở mục 3. Điền giá trị thật cho các ký hiệu [..] ở sheet "Dữ liệu test".</t>
+  </si>
+  <si>
+    <t>Bước 1 – Chuẩn bị dữ liệu</t>
+  </si>
+  <si>
+    <t>Quy trình thực hiện (theo C6-D2)</t>
+  </si>
+  <si>
+    <t>"Phi chức năng": kiểm tra ngoài luồng UC (ví dụ giao diện chống bấm 2 lần)</t>
+  </si>
+  <si>
+    <t>Không bắt buộc</t>
+  </si>
+  <si>
+    <t>Loại bổ sung</t>
+  </si>
+  <si>
+    <t>Black-box theo UC Specification</t>
+  </si>
+  <si>
+    <t>1 / alternative flow trong UC Spec</t>
+  </si>
+  <si>
+    <t>Boundary Value Analysis</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Boundary value</t>
+  </si>
+  <si>
+    <t>Equivalence Partitioning (invalid class)</t>
+  </si>
+  <si>
+    <t>Negative, invalid input</t>
+  </si>
+  <si>
+    <t>Functional test cơ bản</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Happy path (main flow)</t>
+  </si>
+  <si>
+    <t>Kỹ thuật áp dụng</t>
+  </si>
+  <si>
+    <t>Số lượng tối thiểu / UC</t>
+  </si>
+  <si>
+    <t>Loại test case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số test case tối thiểu cho mỗi UC </t>
+  </si>
+  <si>
+    <t>Kiệt – 08/10/2026 (K3); retest 09/10/2026 (K4)</t>
+  </si>
+  <si>
+    <t>Người chạy / ngày chạy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postman (gọi API), MySQL Workbench (kiểm tra dữ liệu), trình duyệt: ghi tên và phiên bản: </t>
+  </si>
+  <si>
+    <t>Công cụ</t>
+  </si>
+  <si>
+    <t>Node.js &gt;= 18; MySQL 8; server chạy tại http://localhost:3000 (API: http://localhost:3000/api)</t>
+  </si>
+  <si>
+    <t>Nền tảng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schema.sql + seed.sql của An (nhận 21:00 04/10/2026) – ghi phiên bản hoặc commit: </t>
+  </si>
+  <si>
+    <t>Phiên bản CSDL / seed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1.0-rc (nhận 21:00 07/10/2026) – ghi tag và commit hash: </t>
+  </si>
+  <si>
+    <t>Phiên bản ứng dụng</t>
+  </si>
+  <si>
+    <t>Môi trường test (điền khi nhận bản v1.0-rc)</t>
+  </si>
+  <si>
+    <t>Duy</t>
+  </si>
+  <si>
+    <t>Hậu</t>
+  </si>
+  <si>
+    <t>Tuấn</t>
+  </si>
+  <si>
+    <t>Thu ngân</t>
+  </si>
+  <si>
+    <t>Lập hóa đơn</t>
+  </si>
+  <si>
+    <t>UC08</t>
+  </si>
+  <si>
+    <t>Xuân An</t>
+  </si>
+  <si>
+    <t>Bếp</t>
+  </si>
+  <si>
+    <t>Đánh dấu hết nguyên liệu</t>
+  </si>
+  <si>
+    <t>UC18</t>
+  </si>
+  <si>
+    <t>Cập nhật trạng thái chế biến</t>
+  </si>
+  <si>
+    <t>UC16</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách đơn hàng (KDS)</t>
+  </si>
+  <si>
+    <t>UC15</t>
+  </si>
+  <si>
+    <t>Kiệt</t>
+  </si>
+  <si>
+    <t>Thanh toán hóa đơn (UC10.1 tiền mặt, UC10.2 QR giả lập)</t>
+  </si>
+  <si>
+    <t>Phục vụ</t>
+  </si>
+  <si>
+    <t>Cập nhật order (gọi thêm, sửa, hủy món)</t>
+  </si>
+  <si>
+    <t>Tạo và gửi order</t>
+  </si>
+  <si>
+    <t>Tất cả</t>
+  </si>
+  <si>
+    <t>Đăng nhập hệ thống</t>
+  </si>
+  <si>
+    <t>Số TC</t>
+  </si>
+  <si>
+    <t>Viết + chạy test</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Actor</t>
+  </si>
+  <si>
+    <t>Tên UC</t>
+  </si>
+  <si>
+    <t>Phạm vi: 8 UC và phân công test (cross-testing: người viết code không tự test)</t>
+  </si>
+  <si>
+    <t>TEST PLAN – Hệ thống quản lý quán cà phê Làn Mây (Nhóm 5)</t>
+  </si>
+  <si>
+    <t>Nhận xét về độ bao phủ</t>
+  </si>
+  <si>
+    <t>Hướng sửa (method / file)</t>
+  </si>
+  <si>
+    <t>Phân tích nguyên nhân</t>
+  </si>
+  <si>
+    <t>Lỗi nghiêm trọng nhất</t>
+  </si>
+  <si>
+    <t>Tổng hợp số liệu</t>
+  </si>
+  <si>
+    <t>3. Khung báo cáo kết quả (mẫu C6-D2), điền ở K4 trước 21:00 09/10</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>Chưa sửa</t>
+  </si>
+  <si>
+    <t>Đã sửa</t>
+  </si>
+  <si>
+    <t>Số bug</t>
+  </si>
+  <si>
+    <t>Mức độ</t>
+  </si>
+  <si>
+    <t>2. Bug theo mức độ nghiêm trọng</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Tổng TC</t>
+  </si>
+  <si>
+    <t>1. Theo loại test case</t>
+  </si>
+  <si>
+    <t>Toàn nhóm (8 UC)</t>
+  </si>
+  <si>
+    <t>TỔNG</t>
+  </si>
+  <si>
+    <t>Tỉ lệ pass (%)</t>
+  </si>
+  <si>
+    <t>Đã chạy</t>
+  </si>
+  <si>
+    <t>Người test</t>
+  </si>
+  <si>
+    <t>TỔNG HỢP KẾT QUẢ KIỂM THỬ</t>
+  </si>
+  <si>
+    <t>Kết quả retest</t>
+  </si>
+  <si>
+    <t>Trạng thái</t>
+  </si>
+  <si>
+    <t>Người sửa</t>
+  </si>
+  <si>
+    <t>Mức độ nghiêm trọng</t>
+  </si>
+  <si>
+    <t>Kết quả mong đợi</t>
+  </si>
+  <si>
+    <t>Kết quả thực tế</t>
+  </si>
+  <si>
+    <t>Bước tái hiện</t>
+  </si>
+  <si>
+    <t>Mô tả lỗi</t>
+  </si>
+  <si>
+    <t>Related TC</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1279,8 +1618,29 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1299,8 +1659,20 @@
         <bgColor rgb="FFED7D31"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1323,12 +1695,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1345,6 +1730,37 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1401,6 +1817,262 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Dữ liệu test"/>
+      <sheetName val="Test Case"/>
+      <sheetName val="Cần xác nhận"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="B2" t="str">
+            <v>UC</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>UC21</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>UC01</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>UC04</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>UC10</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1699,6 +2371,584 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689663C2-C013-4EAA-A00B-255D1FF81DD9}">
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+  </sheetPr>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G5" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A5)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G6" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G7" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A7)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G8" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A8)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G9" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A9)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G10" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A10)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G11" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A11)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="G12" s="3" t="e">
+        <f>COUNTIF('[1]Test Case'!$B:$B,A12)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="17" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>405</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+    </row>
+    <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+    </row>
+    <row r="31" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+    </row>
+    <row r="36" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="39" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="C22:G22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6038F87-EB00-45B1-AC25-57ADB6A4FABB}">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
@@ -3723,4 +4973,619 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF16DF64-E532-43F9-A54C-6B964E0DDE89}">
+  <sheetPr>
+    <tabColor rgb="FF548235"/>
+  </sheetPr>
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="44" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A4,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A5,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A6,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A7,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A8,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A9,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A10,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$B:$B,"TC-"&amp;RIGHT($A11,2)&amp;"-*")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="16">
+        <f>SUM(J4:J11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A25)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A25,'Bug Report'!$I:$I,"Đã retest đạt")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="3">
+        <f>D25-E25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A26)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A26,'Bug Report'!$I:$I,"Đã retest đạt")</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <f>D26-E26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A27)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A27,'Bug Report'!$I:$I,"Đã retest đạt")</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <f>D27-E27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A28)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <f>COUNTIFS('Bug Report'!$A:$A,"BUG-N5-*",'Bug Report'!$G:$G,$A28,'Bug Report'!$I:$I,"Đã retest đạt")</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <f>D28-E28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="B31" s="7" t="str">
+        <f>"Đã chạy "&amp;E12&amp;" / "&amp;D12&amp;" TC; PASS "&amp;F12&amp;"; FAIL "&amp;G12&amp;"; tỉ lệ pass "&amp;IF(E12=0,"-",TEXT(F12/E12,"0.0%"))</f>
+        <v>Đã chạy  /  TC; PASS ; FAIL ; tỉ lệ pass -</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+    </row>
+    <row r="32" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+    </row>
+    <row r="34" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+    </row>
+    <row r="35" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B33:J33"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B35:J35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB17B1A6-CBE5-4654-A4B3-5FD415336E73}">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+  </sheetPr>
+  <dimension ref="A1:J5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40" style="1" customWidth="1"/>
+    <col min="4" max="4" width="46" style="1" customWidth="1"/>
+    <col min="5" max="6" width="34" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="10" width="14" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.7109375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G298" xr:uid="{00000000-0002-0000-0300-000000000000}">
+      <formula1>"Critical,High,Medium,Low"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I2:I298" xr:uid="{00000000-0002-0000-0300-000001000000}">
+      <formula1>"Mới,Đang sửa,Đã sửa,Đã retest đạt,Retest lỗi lại"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>
--- a/tests/testcase.xlsx
+++ b/tests/testcase.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Case" sheetId="2" r:id="rId1"/>
+    <sheet name="Test Case" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$A$1:$O$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="513">
   <si>
     <t>ID</t>
   </si>
@@ -1254,7 +1254,12 @@
     <t>Tồn kho = 10</t>
   </si>
   <si>
-    <t>1. Mở màn hình quản lý kho.2. Nhập số lượng tồn kho nguyên liệu.3. Bấm "Lưu".</t>
+    <t>1. Đăng nhập bằng tài khoản BARISTA hợp lệ và mở màn hình Quản lý kho; nếu kiểm thử API, lấy token hợp lệ và xác định ID nguyên liệu [NL_CA_PHE].
+2. Gọi GET /api/inventory/[NL_CA_PHE] (hoặc endpoint lấy danh sách kho theo contract) để ghi nhận số lượng tồn ban đầu là 10.
+3. Gửi POST /api/inventory/[NL_CA_PHE]/restock với Content-Type: application/json và body {"soLuong":10}.
+4. Kiểm tra HTTP status, trường success, thông tin nguyên liệu và số lượng sau cập nhật trong response.
+5. Gọi lại GET thông tin nguyên liệu; xác nhận tồn kho mới bằng tồn ban đầu + số lượng nhập (10 + 10 = 20).
+6. Làm mới màn hình quản lý kho và xác nhận giao diện hiển thị cùng số lượng 20, không bị cộng lặp khi chỉ tải lại trang.</t>
   </si>
   <si>
     <t>HTTP 200. Hệ thống lưu thành công, món ăn liên quan hiển thị trạng thái đang bán bình thường.</t>
@@ -1272,7 +1277,12 @@
     <t>Tồn kho = 0</t>
   </si>
   <si>
-    <t>1. Mở kho.</t>
+    <t>1. Chuẩn bị nguyên liệu Cà phê [NL_CA_PHE] có số lượng tồn bằng 0; xác nhận qua GET API hoặc dữ liệu seed/CSDL.
+2. Xác định các món trong menu có sử dụng nguyên liệu này và ghi nhận trạng thái trước khi kiểm thử.
+3. Mở màn hình quản lý kho hoặc gọi endpoint đọc menu để tải lại trạng thái các món.
+4. Kiểm tra response API và trạng thái hiển thị trên giao diện đối với từng món phụ thuộc nguyên liệu.
+5. Thử mở màn hình gọi món và tìm món sử dụng Cà phê; không thực hiện tạo đơn thật nếu môi trường dùng dữ liệu chung.
+6. Ghi nhận mã trạng thái/trạng thái món và đối chiếu quy tắc tự động hết hàng khi tồn kho bằng 0.</t>
   </si>
   <si>
     <t>HTTP 200. Các món sử dụng Cà phê tự động khóa (chuyển sang TAM_HET), giao diện chuyển xám.</t>
@@ -1281,12 +1291,6 @@
     <t>Giá trị biên 0.</t>
   </si>
   <si>
-    <t>2. Nhập số lượng tồn kho Cà phê = 0.</t>
-  </si>
-  <si>
-    <t>3. Bấm "Lưu".</t>
-  </si>
-  <si>
     <t>TC-18-03</t>
   </si>
   <si>
@@ -1299,12 +1303,17 @@
     <t>Tồn kho = -5</t>
   </si>
   <si>
+    <t>1. Đăng nhập tài khoản BARISTA hợp lệ hoặc chuẩn bị token hợp lệ; xác định ID nguyên liệu [NL_CA_PHE] đang có tồn kho đã ghi nhận.
+2. Gọi GET thông tin nguyên liệu và lưu lại số lượng ban đầu để so sánh sau kiểm thử.
+3. Gửi POST /api/inventory/[NL_CA_PHE]/restock với Content-Type: application/json và body {"soLuong":-5}.
+4. Kiểm tra HTTP status, success, maLoi và message trong response lỗi.
+5. Gọi lại GET thông tin nguyên liệu; xác nhận số lượng tồn không đổi so với ban đầu.
+6. Kiểm tra giao diện có hiển thị thông báo lỗi phù hợp và không hiển thị nhập kho thành công.</t>
+  </si>
+  <si>
     <t>HTTP 400, maloi=SO_LUONG_KHONG_HOP_LE. Hệ thống chặn cập nhật, thông báo lỗi không được nhập số âm.</t>
   </si>
   <si>
-    <t>2. Nhập số lượng tồn kho Cà phê = -5.</t>
-  </si>
-  <si>
     <t>TC-18-04</t>
   </si>
   <si>
@@ -1317,12 +1326,17 @@
     <t>Tồn kho = rỗng</t>
   </si>
   <si>
+    <t>1. Đăng nhập tài khoản BARISTA hợp lệ hoặc chuẩn bị token hợp lệ; xác định ID nguyên liệu cần kiểm thử.
+2. Ghi lại số lượng tồn hiện tại qua GET API hoặc trên giao diện quản lý kho.
+3. Gửi yêu cầu nhập kho nhưng để trống trường soLuong; nếu API nhận JSON, thử body {} và không tự điền giá trị mặc định.
+4. Kiểm tra HTTP status và các trường success, maLoi, message theo API contract.
+5. Gọi lại GET thông tin nguyên liệu và xác nhận số lượng tồn không bị thay đổi.
+6. Nếu thao tác qua giao diện, để trống ô số lượng rồi bấm Lưu; xác nhận hệ thống báo thiếu dữ liệu và không lưu.</t>
+  </si>
+  <si>
     <t>HTTP 400, maloi=THIEU_THONG_TIN. Hệ thống báo lỗi yêu cầu nhập dữ liệu hợp lệ.</t>
   </si>
   <si>
-    <t>2. Xóa trắng ô nhập tồn kho nguyên liệu.</t>
-  </si>
-  <si>
     <t>TC-18-05</t>
   </si>
   <si>
@@ -1338,15 +1352,20 @@
     <t>Tồn kho = 50</t>
   </si>
   <si>
+    <t>1. Chuẩn bị nguyên liệu Cà phê có tồn kho bằng 0 và món liên quan đang ở trạng thái TAM_HET; ghi nhận trạng thái ban đầu.
+2. Xác nhận trạng thái ban đầu bằng API đọc kho/menu hoặc trên giao diện.
+3. Gửi POST /api/inventory/[NL_CA_PHE]/restock với body {"soLuong":50} và token hợp lệ.
+4. Kiểm tra response thành công và gọi lại API đọc kho để xác nhận số lượng tồn bằng 50.
+5. Tải lại danh sách menu hoặc màn hình gọi món để kiểm tra trạng thái món liên quan.
+6. Xác nhận món được mở bán lại theo quy tắc nghiệp vụ; nếu trạng thái không tự cập nhật, ghi nhận thực tế và đối chiếu contract.</t>
+  </si>
+  <si>
     <t>HTTP 200. Tồn kho cập nhật, món Cà phê tự động mở bán trở lại.</t>
   </si>
   <si>
     <t>Kiểm tra logic nối với màn gọi món.</t>
   </si>
   <si>
-    <t>2. Nhập 50 cho nguyên liệu đang bị khóa.</t>
-  </si>
-  <si>
     <t>TC-16-01</t>
   </si>
   <si>
@@ -1365,15 +1384,17 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>1. Bấm nút DANG_LAM.</t>
+    <t>1. Mở màn hình KDS bằng tài khoản BARISTA và chọn một chi tiết món đang ở trạng thái CHO_PHA_CHE; ghi lại chiTietId.
+2. Xác nhận trạng thái hiện tại trên giao diện và qua API/dữ liệu nếu có quyền truy cập.
+3. Thực hiện thao tác hợp lệ để chuyển món sang trạng thái kế tiếp DANG_LAM.
+4. Kiểm tra request PATCH /api/kitchen/items/[chiTietId]/status gửi đúng body {"trangThai":"DANG_LAM"}.
+5. Kiểm tra HTTP status và response; xác nhận trạng thái trả về là DANG_LAM.
+6. Tải lại KDS hoặc truy vấn lại dữ liệu để xác nhận trạng thái đã được lưu bền vững và chỉ cập nhật đúng món được chọn.</t>
   </si>
   <si>
     <t>HTTP 200. Trạng thái món chuyển đổi thành công trên giao diện và CSDL sau mỗi lần bấm.</t>
   </si>
   <si>
-    <t>2. Bấm tiếp nút DA_XONG.</t>
-  </si>
-  <si>
     <t>TC-16-02</t>
   </si>
   <si>
@@ -1383,7 +1404,12 @@
     <t>Order có nhiều món, các món khác đã DA_XONG</t>
   </si>
   <si>
-    <t>1. Bấm DA_XONG cho món cuối cùng còn lại của Order.</t>
+    <t>1. Chuẩn bị một đơn có nhiều chi tiết món; xác nhận tất cả trừ một món đã ở trạng thái DA_XONG và đơn đang DANG_PHUC_VU.
+2. Ghi lại ID đơn, chiTietId của món cuối và trạng thái hiện tại của đơn/món.
+3. Gửi PATCH /api/kitchen/items/[chiTietId]/status với body {"trangThai":"DA_XONG"}.
+4. Kiểm tra HTTP status, success và dữ liệu trạng thái món trong response.
+5. Gọi lại API đọc đơn/KDS; xác nhận món cuối là DA_XONG và đơn chuyển HOAN_THANH theo quy tắc nghiệp vụ.
+6. Xác nhận các chi tiết món khác không bị thay đổi trạng thái ngoài dự kiến.</t>
   </si>
   <si>
     <t>HTTP 200. Trạng thái của toàn bộ Đơn hàng tự động chuyển từ DANG_PHUC_VU sang HOAN_THANH.</t>
@@ -1401,7 +1427,11 @@
     <t>Món đang ở CHO_PHA_CHE</t>
   </si>
   <si>
-    <t>1. Bấm chuyển thẳng 1 món từ CHO_PHA_CHE sang DA_XONG (Bỏ qua Đang làm).</t>
+    <t>1. Chuẩn bị một chi tiết món đang ở CHO_PHA_CHE và ghi lại chiTietId cùng trạng thái ban đầu.
+2. Gửi trực tiếp PATCH /api/kitchen/items/[chiTietId]/status với body {"trangThai":"DA_XONG"}, bỏ qua trạng thái trung gian.
+3. Kiểm tra HTTP status, success, maLoi và message của response.
+4. Gọi lại API đọc chi tiết món hoặc tải lại KDS để xác nhận trạng thái vẫn là CHO_PHA_CHE.
+5. Xác nhận hệ thống không cập nhật đơn sang trạng thái hoàn thành và không tạo thay đổi dữ liệu ngoài ý muốn.</t>
   </si>
   <si>
     <t>HTTP 400, maloi=TRANG_THAI_KHONG_HOP_LE. Hệ thống chặn thao tác.</t>
@@ -1416,7 +1446,11 @@
     <t>Món đang ở DA_XONG</t>
   </si>
   <si>
-    <t>1. Gửi API lùi trạng thái từ DA_XONG về CHO_PHA_CHE (không qua API hoàn tác).</t>
+    <t>1. Chuẩn bị một chi tiết món đang ở DA_XONG; ghi lại chiTietId và trạng thái ban đầu.
+2. Gửi PATCH /api/kitchen/items/[chiTietId]/status với body {"trangThai":"CHO_PHA_CHE"} để thử lùi trạng thái bằng endpoint thông thường.
+3. Kiểm tra HTTP status, maLoi và message; đối chiếu mã lỗi chuyển trạng thái không hợp lệ theo API contract.
+4. Gọi lại API đọc chi tiết món để xác nhận trạng thái vẫn là DA_XONG.
+5. Không gọi endpoint undo trong test case này; việc hoàn tác được kiểm tra riêng ở TC-16-06.</t>
   </si>
   <si>
     <t>HTTP 400. API từ chối cập nhật lùi trái phép.</t>
@@ -1434,7 +1468,11 @@
     <t>Order có món bị hủy (DA_HUY)</t>
   </si>
   <si>
-    <t>1. Cố gắng bấm nút thao tác cho món có trạng thái DA_HUY.</t>
+    <t>1. Chuẩn bị một đơn có chi tiết món đã bị hủy và có trạng thái DA_HUY; ghi lại chiTietId.
+2. Mở KDS, tìm món đã hủy và quan sát các nút thao tác trạng thái trên giao diện.
+3. Nếu giao diện cho phép gửi request, thử cập nhật bằng PATCH /api/kitchen/items/[chiTietId]/status với body {"trangThai":"DANG_LAM"}.
+4. Kiểm tra HTTP status và maLoi theo contract; với trường hợp MON_DA_HUY, đối chiếu HTTP 409 nếu contract quy định.
+5. Tải lại chi tiết món và xác nhận trạng thái vẫn là DA_HUY, không quay lại luồng pha chế.</t>
   </si>
   <si>
     <t>Giao diện: nút bị khóa. Nếu gọi API thẳng sẽ trả HTTP 400.</t>
@@ -1452,15 +1490,17 @@
     <t>Món vừa chuyển sang DANG_LAM</t>
   </si>
   <si>
-    <t>1. Bấm nhầm món sang DANG_LAM.</t>
+    <t>1. Chuẩn bị một chi tiết món vừa chuyển từ CHO_PHA_CHE sang DANG_LAM; ghi lại chiTietId và thời điểm chuyển trạng thái.
+2. Xác nhận trạng thái hiện tại là DANG_LAM trên KDS/API.
+3. Gửi POST /api/kitchen/items/[chiTietId]/undo theo API contract để yêu cầu hoàn tác thao tác gần nhất.
+4. Kiểm tra HTTP status, success, maLoi và trạng thái món trả về.
+5. Gọi lại API đọc chi tiết món hoặc tải lại KDS; xác nhận trạng thái trở về CHO_PHA_CHE đúng một bước.
+6. Nếu gọi undo khi không có thao tác hợp lệ để hoàn tác, kiểm tra lỗi KHONG_THE_HOAN_TAC theo contract ở một lượt kiểm thử riêng.</t>
   </si>
   <si>
     <t>HTTP 200. Trạng thái lùi đúng 1 bước về lại CHO_PHA_CHE.</t>
   </si>
   <si>
-    <t>2. Bấm nút "Hoàn tác".</t>
-  </si>
-  <si>
     <t>TC-15-01</t>
   </si>
   <si>
@@ -1476,15 +1516,17 @@
     <t>3 Order gửi cách nhau 1 phút</t>
   </si>
   <si>
-    <t>1. Phục vụ gửi liên tiếp 3 Order A, B, C.</t>
+    <t>1. Chuẩn bị môi trường KDS và ba đơn/món A, B, C có trạng thái cần hiển thị; tạo/gửi lần lượt từng đơn cách nhau khoảng một phút.
+2. Ghi lại thời điểm tạo/gửi của từng đơn để xác định thứ tự FIFO mong đợi: A trước B, B trước C.
+3. Đăng nhập tài khoản BARISTA và mở màn hình KDS; gọi GET /api/kitchen/items hoặc tải lại danh sách lần đầu.
+4. Kiểm tra HTTP status và thứ tự các item trong response dựa trên thời điểm tạo.
+5. Đối chiếu thứ tự trên giao diện với response: đơn/món cũ hơn phải xuất hiện trước đơn/món mới hơn.
+6. Chờ chu kỳ polling tiếp theo và xác nhận thứ tự FIFO vẫn đúng, không đảo vị trí bất thường.</t>
   </si>
   <si>
     <t>HTTP 200. Màn hình KDS hiển thị 3 thẻ Order xếp đúng thứ tự FIFO (Order A trên cùng).</t>
   </si>
   <si>
-    <t>2. Bếp mở KDS.</t>
-  </si>
-  <si>
     <t>TC-15-02</t>
   </si>
   <si>
@@ -1497,15 +1539,17 @@
     <t>Quán chưa có order nào</t>
   </si>
   <si>
-    <t>1. Đăng nhập tài khoản Bếp.</t>
+    <t>1. Chuẩn bị môi trường không có món cần xử lý trên KDS: không có đơn mới, hoặc tất cả món đã DA_XONG/DA_HUY theo điều kiện lọc của API.
+2. Đăng nhập tài khoản BARISTA và mở màn hình KDS.
+3. Gọi GET /api/kitchen/items hoặc chờ màn hình tải dữ liệu; kiểm tra HTTP status và kiểu dữ liệu danh sách trả về.
+4. Xác nhận response trả danh sách rỗng hợp lệ, không phải lỗi máy chủ.
+5. Quan sát giao diện và xác nhận hiển thị trạng thái rỗng như “Chưa có order”, không xuất hiện thẻ món cũ.
+6. Chờ ít nhất một chu kỳ polling để xác nhận trạng thái rỗng không làm giao diện treo hoặc phát sinh lỗi.</t>
   </si>
   <si>
     <t>HTTP 200. Danh sách rỗng, giao diện hiện trạng thái "Chưa có order".</t>
   </si>
   <si>
-    <t>2. Mở màn hình KDS.</t>
-  </si>
-  <si>
     <t>TC-15-03</t>
   </si>
   <si>
@@ -1518,15 +1562,17 @@
     <t>"Ít đá, không đường"</t>
   </si>
   <si>
-    <t>1. Phục vụ tạo đơn có ghi chú.</t>
+    <t>1. Tạo một đơn hợp lệ có ít nhất một món và ghi chú đặc biệt “Ít đá, không đường” tại trường ghi chú theo giao diện/API.
+2. Gửi đơn vào bếp và ghi lại mã đơn, chi tiết món cùng nội dung ghi chú đã gửi.
+3. Mở KDS hoặc gọi GET /api/kitchen/items; kiểm tra response có trường ghi chú theo contract.
+4. Tìm đúng thẻ món tương ứng với đơn vừa tạo và đối chiếu nội dung ghi chú với dữ liệu đầu vào.
+5. Xác nhận ghi chú hiển thị đầy đủ, dễ nhận biết, không bị mất dấu tiếng Việt, cắt cụt hoặc gắn nhầm sang món khác.
+6. Chờ lần polling tiếp theo và xác nhận ghi chú vẫn hiển thị đúng.</t>
   </si>
   <si>
     <t>HTTP 200. Ghi chú "Ít đá, không đường" được in đậm/nổi bật trên thẻ tương ứng.</t>
   </si>
   <si>
-    <t>2. Bếp xem thẻ order trên KDS.</t>
-  </si>
-  <si>
     <t>TC-15-04</t>
   </si>
   <si>
@@ -1539,15 +1585,17 @@
     <t>Màn hình KDS đang mở</t>
   </si>
   <si>
-    <t>1. Giữ nguyên màn hình KDS.</t>
+    <t>1. Đăng nhập tài khoản BARISTA, mở KDS và để nguyên trang; không bấm F5 hoặc nút tải lại.
+2. Ghi nhận danh sách món đang hiển thị và thời gian kiểm tra.
+3. Từ tài khoản phục vụ hoặc API, tạo/gửi một đơn mới đủ điều kiện xuất hiện trên KDS.
+4. Chờ khoảng một chu kỳ polling theo thiết kế (khoảng 3 giây), sau đó quan sát danh sách KDS.
+5. Xác nhận đơn mới xuất hiện mà không cần tải lại trang; kiểm tra request GET định kỳ trong Network nếu cần.
+6. Chờ thêm một chu kỳ và xác nhận đơn không bị nhân đôi, dữ liệu cũ vẫn hiển thị đúng.</t>
   </si>
   <si>
     <t>KDS tự động fetch API (mỗi 3s) và hiển thị Order mới không cần tải lại trang F5.</t>
   </si>
   <si>
-    <t>2. Phục vụ gửi Order mới từ máy khác.</t>
-  </si>
-  <si>
     <t>TC-15-05</t>
   </si>
   <si>
@@ -1566,15 +1614,17 @@
     <t>Ngắt mạng</t>
   </si>
   <si>
-    <t>1. Ngắt kết nối WiFi máy tính Bếp.</t>
+    <t>1. Đăng nhập tài khoản BARISTA, mở KDS và xác nhận danh sách tải thành công khi mạng đang hoạt động.
+2. Mở DevTools/Network hoặc chuẩn bị cách ngắt kết nối mạng trên môi trường test.
+3. Ngắt mạng hoặc chặn request API KDS để mô phỏng lỗi kết nối; không xóa dữ liệu đang hiển thị.
+4. Chờ chu kỳ polling kế tiếp và quan sát phản hồi giao diện khi request thất bại.
+5. Xác nhận giao diện hiển thị thông báo mất kết nối/lỗi tải dữ liệu theo thiết kế, không bị treo hoặc trắng trang.
+6. Khôi phục mạng, chờ polling tiếp theo và xác nhận dữ liệu được tải lại; ghi rõ nếu contract/UI chưa quy định thông báo cụ thể.</t>
   </si>
   <si>
     <t>Giao diện hiện toast thông báo "Mất kết nối".</t>
   </si>
   <si>
-    <t>2. Đợi 3 giây.</t>
-  </si>
-  <si>
     <t>TC-08-01</t>
   </si>
   <si>
@@ -1593,7 +1643,12 @@
     <t>Bàn = 01</t>
   </si>
   <si>
-    <t>1. Thu ngân chọn lập hóa đơn cho Bàn 01.</t>
+    <t>1. Đăng nhập bằng tài khoản THU_NGAN hợp lệ và chọn bàn/đơn có đơn hàng tồn tại, đã gửi bếp và chưa thanh toán.
+2. Ghi lại donHangId; xác nhận đơn có ít nhất một món và trạng thái phù hợp để lập hóa đơn.
+3. Gửi GET /api/orders/[donHangId]/invoice hoặc thao tác lập/xem hóa đơn trên POS.
+4. Kiểm tra HTTP 200, success và cấu trúc HoaDonDTO trong response.
+5. Đối chiếu từng dòng dsMon: tên món, số lượng, đơn giá và thành tiền; tự tính tổng các dòng để so sánh tongTien.
+6. Xác nhận tienGiamGia bằng 0 nếu không có khuyến mãi và canThanhToan = tongTien - tienGiamGia; so sánh với số tiền hiển thị trên POS.</t>
   </si>
   <si>
     <t>HTTP 200. Trả về HoaDonDTO: ds món, tổng tiền, giảm giá=0, cần thanh toán=tổng tiền.</t>
@@ -1614,7 +1669,11 @@
     <t>Bàn = 02</t>
   </si>
   <si>
-    <t>1. Thu ngân cố tình gọi API lập hóa đơn cho Bàn 02.</t>
+    <t>1. Đăng nhập tài khoản THU_NGAN hợp lệ và xác nhận Bàn 02 đang trống, không gắn với đơn hàng đang hoạt động.
+2. Gửi GET /api/orders/[ID_KHONG_TON_TAI]/invoice với ID đơn không tồn tại; nếu kiểm tra nghiệp vụ bàn trống qua UI thì chọn chức năng lập hóa đơn cho bàn đó.
+3. Kiểm tra HTTP status, success, maLoi, message và cấu trúc response lỗi theo API contract.
+4. Xác nhận hệ thống trả lỗi phù hợp cho đơn không tồn tại/bàn không có đơn; không nhận được HoaDonDTO hợp lệ.
+5. Tải lại danh sách bàn/đơn và xác nhận không phát sinh hóa đơn, không đổi trạng thái bàn hoặc đơn.</t>
   </si>
   <si>
     <t>HTTP 400, maloi=BAN_KHONG_CO_DON. Hệ thống chặn.</t>
@@ -1632,7 +1691,12 @@
     <t>Bàn = 03</t>
   </si>
   <si>
-    <t>1. Thu ngân bấm lập hóa đơn cho Bàn 03.</t>
+    <t>1. Chuẩn bị một đơn có món đã thêm trên POS nhưng chưa gửi bếp; xác nhận isSynced=false và ghi lại donHangId.
+2. Đăng nhập tài khoản THU_NGAN và mở chức năng lập hóa đơn cho đơn đã chuẩn bị.
+3. Gửi GET /api/orders/[donHangId]/invoice theo contract.
+4. Kiểm tra HTTP status, success, maLoi và message; đối chiếu lỗi DON_CHUA_GUI_BEP theo API contract.
+5. Xác nhận response không trả HoaDonDTO để thanh toán và giao diện không cho tiếp tục thu tiền.
+6. Kiểm tra trạng thái đơn và các chi tiết món vẫn giữ nguyên sau yêu cầu bị từ chối.</t>
   </si>
   <si>
     <t>HTTP 400, maloi=DON_CHUA_GUI_BEP.</t>
@@ -1653,7 +1717,12 @@
     <t>giamGia=10</t>
   </si>
   <si>
-    <t>1. Lập hóa đơn cho Bàn 04 (có áp mã giảm giá).</t>
+    <t>1. Chuẩn bị đơn hợp lệ có áp dụng khuyến mãi/giảm giá 10% theo cấu hình đã được nhóm xác nhận; ghi lại quy tắc tính giảm giá.
+2. Xác nhận đơn đã gửi bếp, chưa thanh toán và có tongTien xác định trước khi mở hóa đơn.
+3. Gửi GET /api/orders/[DON_KHUYEN_MAI]/invoice hoặc mở hóa đơn trên POS.
+4. Kiểm tra HTTP 200 và ghi lại tongTien, tienGiamGia, canThanhToan trong HoaDonDTO.
+5. Tính lại canThanhToan = tongTien - tienGiamGia; nếu quy tắc 10% được hỗ trợ, kiểm tra tienGiamGia theo đúng quy tắc làm tròn đã thống nhất.
+6. Đối chiếu số tiền trên giao diện với DTO. Nếu API contract chưa định nghĩa cơ chế giảm giá, ghi nhận đây là điểm cần xác nhận, không tự kết luận tính năng đã được hỗ trợ.</t>
   </si>
   <si>
     <t>HTTP 200. HoaDonDTO tính chính xác: Cần thanh toán = Tổng tiền - Giảm giá.</t>
@@ -1674,7 +1743,12 @@
     <t>Tổng &gt; 10 triệu</t>
   </si>
   <si>
-    <t>1. Thu ngân lập hóa đơn cho bàn có tổng tiền &gt; 10.000.000đ.</t>
+    <t>1. Chuẩn bị đơn VIP có nhiều món/số lượng để tổng thành tiền vượt 10.000.000 VNĐ; xác nhận đơn đã gửi bếp và chưa thanh toán.
+2. Ghi lại donHangId, số lượng, đơn giá và thành tiền từng dòng để có thể tính lại tổng.
+3. Gửi GET /api/orders/[DON_TIEN_LON]/invoice hoặc mở hóa đơn trên POS.
+4. Kiểm tra HTTP 200, cấu trúc HoaDonDTO và các trường tongTien, tienGiamGia, canThanhToan.
+5. Tính tổng các thành tiền từng dòng và đối chiếu với tongTien; kiểm tra canThanhToan theo công thức tổng tiền trừ giảm giá.
+6. Quan sát hóa đơn ở kích thước cửa sổ thông thường; xác nhận số tiền không bị cắt/tràn và định dạng VNĐ dễ đọc.</t>
   </si>
   <si>
     <t>HTTP 200. Giao diện hiển thị không bị tràn, định dạng đúng tiền tệ (VNĐ).</t>
@@ -1689,7 +1763,12 @@
     <t>Đang xem hóa đơn hợp lệ</t>
   </si>
   <si>
-    <t>1. Bấm nút Thanh toán.</t>
+    <t>1. Mở hóa đơn hợp lệ của đơn đã gửi bếp và chưa thanh toán; ghi lại canThanhToan từ HoaDonDTO.
+2. Bấm nút “Thanh toán” trên POS để mở popup xác nhận.
+3. Kiểm tra popup hiển thị đúng mã/đơn cần thanh toán và số tiền cần thu bằng canThanhToan.
+4. Kiểm tra các phương thức thanh toán được hiển thị theo thiết kế, ví dụ TIEN_MAT hoặc QR; xác nhận trường nhập thay đổi phù hợp với phương thức được chọn.
+5. Đối chiếu số tiền giữa popup và hóa đơn, bảo đảm không tự cộng/trừ thêm khi chỉ mở popup.
+6. Đóng popup hoặc chọn Hủy; xác nhận thao tác chỉ mở popup không làm đơn chuyển DA_THANH_TOAN và không tạo giao dịch thanh toán.</t>
   </si>
   <si>
     <t>Popup thanh toán hiện ra với đúng tổng tiền cần thu từ HoaDonDTO.</t>
@@ -1705,7 +1784,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1738,26 +1817,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2110,7 +2169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2130,58 +2189,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFC4C7C5"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFC4C7C5"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFC4C7C5"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFC4C7C5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2286,153 +2293,153 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2450,21 +2457,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -2830,26 +2827,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O99"/>
   <sheetFormatPr defaultColWidth="8.71296296296296" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="1" customWidth="1"/>
-    <col min="3" max="3" width="60.5555555555556" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34" style="1" customWidth="1"/>
-    <col min="10" max="10" width="50" style="1" customWidth="1"/>
-    <col min="11" max="11" width="52" style="1" customWidth="1"/>
-    <col min="12" max="12" width="30" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="6" width="31" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29" style="1" customWidth="1"/>
+    <col min="10" max="10" width="62" style="1" customWidth="1"/>
+    <col min="11" max="11" width="50" style="1" customWidth="1"/>
+    <col min="12" max="12" width="28" style="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18" style="1" customWidth="1"/>
     <col min="15" max="15" width="34" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.71296296296296" style="1"/>
+    <col min="16" max="16384" width="8.71296296296296" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1" spans="1:15">
@@ -2940,7 +2938,7 @@
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
     </row>
-    <row r="3" ht="66" spans="1:15">
+    <row r="3" ht="66" customHeight="1" spans="1:15">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -2983,7 +2981,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" ht="52.8" spans="1:15">
+    <row r="4" ht="52.8" customHeight="1" spans="1:15">
       <c r="A4" s="4" t="s">
         <v>35</v>
       </c>
@@ -3024,7 +3022,7 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" ht="39.6" spans="1:15">
+    <row r="5" ht="39.6" customHeight="1" spans="1:15">
       <c r="A5" s="4" t="s">
         <v>44</v>
       </c>
@@ -3065,7 +3063,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" ht="66" spans="1:15">
+    <row r="6" ht="66" customHeight="1" spans="1:15">
       <c r="A6" s="4" t="s">
         <v>51</v>
       </c>
@@ -3151,7 +3149,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" ht="39.6" spans="1:15">
+    <row r="8" ht="39.6" customHeight="1" spans="1:15">
       <c r="A8" s="4" t="s">
         <v>68</v>
       </c>
@@ -3194,7 +3192,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" ht="39.6" spans="1:15">
+    <row r="9" ht="39.6" customHeight="1" spans="1:15">
       <c r="A9" s="4" t="s">
         <v>76</v>
       </c>
@@ -3237,7 +3235,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" ht="39.6" spans="1:15">
+    <row r="10" ht="39.6" customHeight="1" spans="1:15">
       <c r="A10" s="4" t="s">
         <v>87</v>
       </c>
@@ -3280,7 +3278,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" ht="39.6" spans="1:15">
+    <row r="11" ht="39.6" customHeight="1" spans="1:15">
       <c r="A11" s="4" t="s">
         <v>96</v>
       </c>
@@ -3366,7 +3364,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" ht="79.2" spans="1:15">
+    <row r="13" ht="79.2" customHeight="1" spans="1:15">
       <c r="A13" s="4" t="s">
         <v>114</v>
       </c>
@@ -3407,7 +3405,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" ht="39.6" spans="1:15">
+    <row r="14" ht="39.6" customHeight="1" spans="1:15">
       <c r="A14" s="4" t="s">
         <v>122</v>
       </c>
@@ -3448,7 +3446,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" ht="39.6" spans="1:15">
+    <row r="15" ht="39.6" customHeight="1" spans="1:15">
       <c r="A15" s="4" t="s">
         <v>129</v>
       </c>
@@ -3489,7 +3487,7 @@
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
     </row>
-    <row r="16" ht="52.8" spans="1:15">
+    <row r="16" ht="52.8" customHeight="1" spans="1:15">
       <c r="A16" s="4" t="s">
         <v>135</v>
       </c>
@@ -3571,7 +3569,7 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
     </row>
-    <row r="18" ht="52.8" spans="1:15">
+    <row r="18" ht="52.8" customHeight="1" spans="1:15">
       <c r="A18" s="4" t="s">
         <v>148</v>
       </c>
@@ -3612,7 +3610,7 @@
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
     </row>
-    <row r="19" ht="52.8" spans="1:15">
+    <row r="19" ht="52.8" customHeight="1" spans="1:15">
       <c r="A19" s="4" t="s">
         <v>155</v>
       </c>
@@ -3655,7 +3653,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" ht="39.6" spans="1:15">
+    <row r="20" ht="39.6" customHeight="1" spans="1:15">
       <c r="A20" s="4" t="s">
         <v>164</v>
       </c>
@@ -3696,7 +3694,7 @@
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
     </row>
-    <row r="21" ht="52.8" spans="1:15">
+    <row r="21" ht="52.8" customHeight="1" spans="1:15">
       <c r="A21" s="4" t="s">
         <v>171</v>
       </c>
@@ -3782,7 +3780,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="23" ht="39.6" spans="1:15">
+    <row r="23" ht="39.6" customHeight="1" spans="1:15">
       <c r="A23" s="4" t="s">
         <v>189</v>
       </c>
@@ -3823,7 +3821,7 @@
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
     </row>
-    <row r="24" ht="66" spans="1:15">
+    <row r="24" ht="66" customHeight="1" spans="1:15">
       <c r="A24" s="4" t="s">
         <v>196</v>
       </c>
@@ -3864,7 +3862,7 @@
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
     </row>
-    <row r="25" ht="52.8" spans="1:15">
+    <row r="25" ht="52.8" customHeight="1" spans="1:15">
       <c r="A25" s="4" t="s">
         <v>204</v>
       </c>
@@ -3905,7 +3903,7 @@
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
     </row>
-    <row r="26" ht="52.8" spans="1:15">
+    <row r="26" ht="52.8" customHeight="1" spans="1:15">
       <c r="A26" s="4" t="s">
         <v>211</v>
       </c>
@@ -3946,7 +3944,7 @@
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
     </row>
-    <row r="27" ht="52.8" spans="1:15">
+    <row r="27" ht="52.8" customHeight="1" spans="1:15">
       <c r="A27" s="4" t="s">
         <v>217</v>
       </c>
@@ -3987,7 +3985,7 @@
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
     </row>
-    <row r="28" ht="52.8" spans="1:15">
+    <row r="28" ht="52.8" customHeight="1" spans="1:15">
       <c r="A28" s="4" t="s">
         <v>223</v>
       </c>
@@ -4069,7 +4067,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" ht="52.8" spans="1:15">
+    <row r="30" ht="52.8" customHeight="1" spans="1:15">
       <c r="A30" s="4" t="s">
         <v>234</v>
       </c>
@@ -4110,7 +4108,7 @@
       <c r="N30" s="6"/>
       <c r="O30" s="6"/>
     </row>
-    <row r="31" ht="66" spans="1:15">
+    <row r="31" ht="66" customHeight="1" spans="1:15">
       <c r="A31" s="4" t="s">
         <v>239</v>
       </c>
@@ -4194,7 +4192,7 @@
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
     </row>
-    <row r="33" ht="66" spans="1:15">
+    <row r="33" ht="66" customHeight="1" spans="1:15">
       <c r="A33" s="4" t="s">
         <v>253</v>
       </c>
@@ -4235,7 +4233,7 @@
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
     </row>
-    <row r="34" ht="66" spans="1:15">
+    <row r="34" ht="66" customHeight="1" spans="1:15">
       <c r="A34" s="4" t="s">
         <v>259</v>
       </c>
@@ -4317,7 +4315,7 @@
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
     </row>
-    <row r="36" ht="66" spans="1:15">
+    <row r="36" ht="66" customHeight="1" spans="1:15">
       <c r="A36" s="4" t="s">
         <v>274</v>
       </c>
@@ -4358,7 +4356,7 @@
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
     </row>
-    <row r="37" ht="92.4" spans="1:15">
+    <row r="37" ht="92.4" customHeight="1" spans="1:15">
       <c r="A37" s="4" t="s">
         <v>281</v>
       </c>
@@ -4442,7 +4440,7 @@
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
     </row>
-    <row r="39" ht="52.8" spans="1:15">
+    <row r="39" ht="52.8" customHeight="1" spans="1:15">
       <c r="A39" s="4" t="s">
         <v>297</v>
       </c>
@@ -4483,7 +4481,7 @@
       <c r="N39" s="6"/>
       <c r="O39" s="6"/>
     </row>
-    <row r="40" ht="52.8" spans="1:15">
+    <row r="40" ht="52.8" customHeight="1" spans="1:15">
       <c r="A40" s="4" t="s">
         <v>304</v>
       </c>
@@ -4567,7 +4565,7 @@
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
     </row>
-    <row r="42" ht="52.8" spans="1:15">
+    <row r="42" ht="52.8" customHeight="1" spans="1:15">
       <c r="A42" s="4" t="s">
         <v>319</v>
       </c>
@@ -4610,7 +4608,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="43" ht="66" spans="1:15">
+    <row r="43" ht="66" customHeight="1" spans="1:15">
       <c r="A43" s="4" t="s">
         <v>327</v>
       </c>
@@ -4692,7 +4690,7 @@
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
     </row>
-    <row r="45" ht="39.6" spans="1:15">
+    <row r="45" ht="39.6" customHeight="1" spans="1:15">
       <c r="A45" s="4" t="s">
         <v>341</v>
       </c>
@@ -4735,7 +4733,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="46" ht="66" spans="1:15">
+    <row r="46" ht="66" customHeight="1" spans="1:15">
       <c r="A46" s="4" t="s">
         <v>350</v>
       </c>
@@ -4778,7 +4776,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="47" ht="66.75" spans="1:15">
+    <row r="47" ht="66.75" customHeight="1" spans="1:15">
       <c r="A47" s="4" t="s">
         <v>359</v>
       </c>
@@ -4821,47 +4819,49 @@
         <v>367</v>
       </c>
     </row>
-    <row r="48" ht="28.35" spans="1:15">
+    <row r="48" ht="190" customHeight="1" spans="1:15">
       <c r="A48" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="I48" s="7" t="s">
+      <c r="I48" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="J48" s="7" t="s">
+      <c r="J48" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-    </row>
-    <row r="49" ht="15.15" spans="1:15">
-      <c r="A49" s="8" t="s">
+      <c r="L48" s="8"/>
+      <c r="M48" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+    </row>
+    <row r="49" ht="190" customHeight="1" spans="1:15">
+      <c r="A49" s="7" t="s">
         <v>377</v>
       </c>
       <c r="B49" s="8" t="s">
@@ -4879,7 +4879,7 @@
       <c r="F49" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H49" s="8" t="s">
@@ -4888,435 +4888,813 @@
       <c r="I49" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="8" t="s">
         <v>381</v>
       </c>
       <c r="K49" s="8" t="s">
         <v>382</v>
       </c>
       <c r="L49" s="8"/>
-      <c r="M49" s="8"/>
+      <c r="M49" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N49" s="8"/>
       <c r="O49" s="8" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="50" ht="15.15" spans="1:15">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="8"/>
+    <row r="50" ht="170" customHeight="1" spans="1:15">
+      <c r="A50" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>389</v>
+      </c>
       <c r="L50" s="8"/>
-      <c r="M50" s="8"/>
+      <c r="M50" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
     </row>
-    <row r="51" ht="15.15" spans="1:15">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="K51" s="8"/>
+    <row r="51" ht="170" customHeight="1" spans="1:15">
+      <c r="A51" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>395</v>
+      </c>
       <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
+      <c r="M51" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
     </row>
-    <row r="52" ht="15.15" spans="1:15">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="8"/>
+    <row r="52" ht="170" customHeight="1" spans="1:15">
+      <c r="A52" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="J52" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>402</v>
+      </c>
       <c r="L52" s="8"/>
-      <c r="M52" s="8"/>
+      <c r="M52" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-    </row>
-    <row r="53" ht="15.15" spans="1:15">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="K53" s="8"/>
+      <c r="O52" s="8" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="53" ht="170" customHeight="1" spans="1:15">
+      <c r="A53" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>411</v>
+      </c>
       <c r="L53" s="8"/>
-      <c r="M53" s="8"/>
+      <c r="M53" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
     </row>
-    <row r="54" ht="15.15" spans="1:15">
-      <c r="A54" s="8" t="s">
-        <v>386</v>
+    <row r="54" ht="190" customHeight="1" spans="1:15">
+      <c r="A54" s="7" t="s">
+        <v>412</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="G54" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>381</v>
+        <v>409</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>415</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="L54" s="8"/>
-      <c r="M54" s="8"/>
+      <c r="M54" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
     </row>
-    <row r="55" ht="15.15" spans="1:15">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="8"/>
+    <row r="55" ht="170" customHeight="1" spans="1:15">
+      <c r="A55" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="K55" s="8" t="s">
+        <v>422</v>
+      </c>
       <c r="L55" s="8"/>
-      <c r="M55" s="8"/>
+      <c r="M55" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
     </row>
-    <row r="56" ht="15.15" spans="1:15">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8"/>
-      <c r="J56" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="K56" s="8"/>
+    <row r="56" ht="170" customHeight="1" spans="1:15">
+      <c r="A56" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>427</v>
+      </c>
       <c r="L56" s="8"/>
-      <c r="M56" s="8"/>
+      <c r="M56" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-    </row>
-    <row r="57" ht="15.15" spans="1:15">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="8"/>
+      <c r="O56" s="8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="57" ht="170" customHeight="1" spans="1:15">
+      <c r="A57" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>433</v>
+      </c>
       <c r="L57" s="8"/>
-      <c r="M57" s="8"/>
+      <c r="M57" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N57" s="8"/>
       <c r="O57" s="8"/>
     </row>
-    <row r="58" ht="15.15" spans="1:15">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="K58" s="8"/>
+    <row r="58" ht="170" customHeight="1" spans="1:15">
+      <c r="A58" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>439</v>
+      </c>
       <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
+      <c r="M58" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N58" s="8"/>
       <c r="O58" s="8"/>
     </row>
-    <row r="59" ht="15.15" spans="1:15">
-      <c r="A59" s="8" t="s">
-        <v>392</v>
+    <row r="59" ht="190" customHeight="1" spans="1:15">
+      <c r="A59" s="7" t="s">
+        <v>440</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>369</v>
+        <v>441</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>47</v>
+        <v>443</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="H59" s="8" t="s">
         <v>373</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>381</v>
+        <v>444</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>445</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
+      <c r="M59" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N59" s="8"/>
       <c r="O59" s="8"/>
     </row>
-    <row r="60" ht="15.15" spans="1:15">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="8"/>
+    <row r="60" ht="170" customHeight="1" spans="1:15">
+      <c r="A60" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>452</v>
+      </c>
       <c r="L60" s="8"/>
-      <c r="M60" s="8"/>
+      <c r="M60" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N60" s="8"/>
       <c r="O60" s="8"/>
     </row>
-    <row r="61" ht="15.15" spans="1:15">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="K61" s="8"/>
+    <row r="61" ht="170" customHeight="1" spans="1:15">
+      <c r="A61" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K61" s="8" t="s">
+        <v>458</v>
+      </c>
       <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
+      <c r="M61" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N61" s="8"/>
       <c r="O61" s="8"/>
     </row>
-    <row r="62" ht="15.15" spans="1:15">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="8"/>
+    <row r="62" ht="170" customHeight="1" spans="1:15">
+      <c r="A62" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="J62" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K62" s="8" t="s">
+        <v>464</v>
+      </c>
       <c r="L62" s="8"/>
-      <c r="M62" s="8"/>
+      <c r="M62" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N62" s="8"/>
       <c r="O62" s="8"/>
     </row>
-    <row r="63" ht="15.15" spans="1:15">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="K63" s="8"/>
+    <row r="63" ht="170" customHeight="1" spans="1:15">
+      <c r="A63" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>472</v>
+      </c>
       <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
+      <c r="M63" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N63" s="8"/>
       <c r="O63" s="8"/>
     </row>
-    <row r="64" ht="15.15" spans="1:15">
-      <c r="A64" s="8" t="s">
-        <v>398</v>
+    <row r="64" ht="190" customHeight="1" spans="1:15">
+      <c r="A64" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>369</v>
+        <v>474</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>371</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="G64" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="G64" s="5" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>401</v>
+        <v>477</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>381</v>
+        <v>478</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>479</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>403</v>
+        <v>480</v>
       </c>
       <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
+      <c r="M64" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N64" s="8"/>
-      <c r="O64" s="8" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="65" ht="15.15" spans="1:15">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="8"/>
+      <c r="O64" s="8"/>
+    </row>
+    <row r="65" ht="170" customHeight="1" spans="1:15">
+      <c r="A65" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>487</v>
+      </c>
       <c r="L65" s="8"/>
-      <c r="M65" s="8"/>
+      <c r="M65" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N65" s="8"/>
       <c r="O65" s="8"/>
     </row>
-    <row r="66" ht="15.15" spans="1:15">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="K66" s="8"/>
+    <row r="66" ht="170" customHeight="1" spans="1:15">
+      <c r="A66" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="J66" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="K66" s="8" t="s">
+        <v>493</v>
+      </c>
       <c r="L66" s="8"/>
-      <c r="M66" s="8"/>
+      <c r="M66" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N66" s="8"/>
       <c r="O66" s="8"/>
     </row>
-    <row r="67" ht="15.15" spans="1:15">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="8"/>
+    <row r="67" ht="190" customHeight="1" spans="1:15">
+      <c r="A67" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="J67" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="K67" s="8" t="s">
+        <v>500</v>
+      </c>
       <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
+      <c r="M67" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N67" s="8"/>
       <c r="O67" s="8"/>
     </row>
-    <row r="68" ht="15.15" spans="1:15">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="K68" s="8"/>
+    <row r="68" ht="170" customHeight="1" spans="1:15">
+      <c r="A68" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>507</v>
+      </c>
       <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
+      <c r="M68" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N68" s="8"/>
       <c r="O68" s="8"/>
     </row>
-    <row r="69" ht="15.15" spans="1:15">
-      <c r="A69" s="8" t="s">
-        <v>406</v>
+    <row r="69" ht="170" customHeight="1" spans="1:15">
+      <c r="A69" s="7" t="s">
+        <v>508</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>407</v>
+        <v>474</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>408</v>
+        <v>509</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>18</v>
@@ -5325,1066 +5703,64 @@
         <v>371</v>
       </c>
       <c r="F69" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="I69" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="G69" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="I69" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>412</v>
+      <c r="J69" s="8" t="s">
+        <v>511</v>
       </c>
       <c r="K69" s="8" t="s">
-        <v>413</v>
+        <v>512</v>
       </c>
       <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
+      <c r="M69" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="N69" s="8"/>
       <c r="O69" s="8"/>
     </row>
-    <row r="70" ht="15.15" spans="1:15">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
-    </row>
-    <row r="71" ht="15.15" spans="1:15">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
-    </row>
-    <row r="72" ht="28.35" spans="1:15">
-      <c r="A72" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="D72" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F72" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="K72" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-    </row>
-    <row r="73" ht="28.35" spans="1:15">
-      <c r="A73" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="D73" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="I73" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="K73" s="8" t="s">
-        <v>425</v>
-      </c>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
-    </row>
-    <row r="74" ht="28.35" spans="1:15">
-      <c r="A74" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F74" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="K74" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="75" ht="28.35" spans="1:15">
-      <c r="A75" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>433</v>
-      </c>
-      <c r="D75" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F75" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="I75" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J75" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="K75" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
-      <c r="N75" s="8"/>
-      <c r="O75" s="8"/>
-    </row>
-    <row r="76" ht="15.15" spans="1:15">
-      <c r="A76" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>438</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>440</v>
-      </c>
-      <c r="I76" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J76" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="K76" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
-      <c r="N76" s="8"/>
-      <c r="O76" s="8"/>
-    </row>
-    <row r="77" ht="15.15" spans="1:15">
-      <c r="A77" s="8"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
-      <c r="N77" s="8"/>
-      <c r="O77" s="8"/>
-    </row>
-    <row r="78" ht="15.15" spans="1:15">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="12" t="s">
-        <v>443</v>
-      </c>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
-      <c r="N78" s="8"/>
-      <c r="O78" s="8"/>
-    </row>
-    <row r="79" ht="15.15" spans="1:15">
-      <c r="A79" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="D79" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F79" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="I79" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="J79" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="K79" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
-      <c r="N79" s="8"/>
-      <c r="O79" s="8"/>
-    </row>
-    <row r="80" ht="15.15" spans="1:15">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
-      <c r="M80" s="8"/>
-      <c r="N80" s="8"/>
-      <c r="O80" s="8"/>
-    </row>
-    <row r="81" ht="15.15" spans="1:15">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
-      <c r="M81" s="8"/>
-      <c r="N81" s="8"/>
-      <c r="O81" s="8"/>
-    </row>
-    <row r="82" ht="15.15" spans="1:15">
-      <c r="A82" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F82" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J82" s="9" t="s">
-        <v>456</v>
-      </c>
-      <c r="K82" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
-    </row>
-    <row r="83" ht="15.15" spans="1:15">
-      <c r="A83" s="8"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="M83" s="8"/>
-      <c r="N83" s="8"/>
-      <c r="O83" s="8"/>
-    </row>
-    <row r="84" ht="15.15" spans="1:15">
-      <c r="A84" s="8"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8"/>
-      <c r="J84" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="M84" s="8"/>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
-    </row>
-    <row r="85" ht="15.15" spans="1:15">
-      <c r="A85" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F85" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="I85" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="J85" s="9" t="s">
-        <v>463</v>
-      </c>
-      <c r="K85" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="L85" s="8"/>
-      <c r="M85" s="8"/>
-      <c r="N85" s="8"/>
-      <c r="O85" s="8"/>
-    </row>
-    <row r="86" ht="15.15" spans="1:15">
-      <c r="A86" s="8"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="M86" s="8"/>
-      <c r="N86" s="8"/>
-      <c r="O86" s="8"/>
-    </row>
-    <row r="87" ht="15.15" spans="1:15">
-      <c r="A87" s="8"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="8"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8"/>
-      <c r="J87" s="12" t="s">
-        <v>465</v>
-      </c>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="M87" s="8"/>
-      <c r="N87" s="8"/>
-      <c r="O87" s="8"/>
-    </row>
-    <row r="88" ht="15.15" spans="1:15">
-      <c r="A88" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H88" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="I88" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J88" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="K88" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="L88" s="8"/>
-      <c r="M88" s="8"/>
-      <c r="N88" s="8"/>
-      <c r="O88" s="8"/>
-    </row>
-    <row r="89" ht="15.15" spans="1:15">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="M89" s="8"/>
-      <c r="N89" s="8"/>
-      <c r="O89" s="8"/>
-    </row>
-    <row r="90" ht="15.15" spans="1:15">
-      <c r="A90" s="8"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="12" t="s">
-        <v>472</v>
-      </c>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
-      <c r="N90" s="8"/>
-      <c r="O90" s="8"/>
-    </row>
-    <row r="91" ht="15.15" spans="1:15">
-      <c r="A91" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="D91" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="F91" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="I91" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="J91" s="9" t="s">
-        <v>479</v>
-      </c>
-      <c r="K91" s="8" t="s">
-        <v>480</v>
-      </c>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-      <c r="N91" s="8"/>
-      <c r="O91" s="8"/>
-    </row>
-    <row r="92" ht="15.15" spans="1:15">
-      <c r="A92" s="8"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="8"/>
-      <c r="N92" s="8"/>
-      <c r="O92" s="8"/>
-    </row>
-    <row r="93" ht="15.15" spans="1:15">
-      <c r="A93" s="8"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-      <c r="N93" s="8"/>
-      <c r="O93" s="8"/>
-    </row>
-    <row r="94" ht="28.35" spans="1:15">
-      <c r="A94" s="8" t="s">
-        <v>482</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F94" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H94" s="8" t="s">
-        <v>486</v>
-      </c>
-      <c r="I94" s="8" t="s">
-        <v>487</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>488</v>
-      </c>
-      <c r="K94" s="8" t="s">
-        <v>489</v>
-      </c>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-      <c r="N94" s="8"/>
-      <c r="O94" s="8"/>
-    </row>
-    <row r="95" ht="28.35" spans="1:15">
-      <c r="A95" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>491</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>394</v>
-      </c>
-      <c r="F95" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H95" s="8" t="s">
-        <v>493</v>
-      </c>
-      <c r="I95" s="8" t="s">
-        <v>494</v>
-      </c>
-      <c r="J95" s="8" t="s">
-        <v>495</v>
-      </c>
-      <c r="K95" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-      <c r="N95" s="8"/>
-      <c r="O95" s="8"/>
-    </row>
-    <row r="96" ht="28.35" spans="1:15">
-      <c r="A96" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F96" s="8" t="s">
-        <v>492</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="I96" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="J96" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="K96" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-      <c r="N96" s="8"/>
-      <c r="O96" s="8"/>
-    </row>
-    <row r="97" ht="28.35" spans="1:15">
-      <c r="A97" s="8" t="s">
-        <v>503</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="D97" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F97" s="8" t="s">
-        <v>505</v>
-      </c>
-      <c r="G97" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>506</v>
-      </c>
-      <c r="I97" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="J97" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="K97" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
-      <c r="O97" s="8"/>
-    </row>
-    <row r="98" ht="28.35" spans="1:15">
-      <c r="A98" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>511</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="F98" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="I98" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="K98" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-    </row>
-    <row r="99" ht="28.35" spans="1:15">
-      <c r="A99" s="8" t="s">
-        <v>517</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>518</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F99" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="G99" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H99" s="8" t="s">
-        <v>519</v>
-      </c>
-      <c r="I99" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="J99" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="K99" s="8" t="s">
-        <v>521</v>
-      </c>
-      <c r="L99" s="8"/>
-      <c r="M99"/>
-      <c r="N99"/>
-      <c r="O99"/>
-    </row>
+    <row r="70" ht="30" customHeight="1"/>
+    <row r="71" ht="105" customHeight="1"/>
+    <row r="72" ht="120" customHeight="1"/>
+    <row r="73" ht="90" customHeight="1"/>
+    <row r="74" ht="90" customHeight="1"/>
+    <row r="75" ht="105" customHeight="1"/>
+    <row r="76" ht="45" customHeight="1"/>
+    <row r="77" ht="45" customHeight="1"/>
+    <row r="78" ht="75" customHeight="1"/>
+    <row r="79" ht="45" customHeight="1"/>
+    <row r="80" ht="30" customHeight="1"/>
+    <row r="81" ht="60" customHeight="1"/>
+    <row r="82" ht="45" customHeight="1"/>
+    <row r="83" ht="30" customHeight="1"/>
+    <row r="84" ht="30" customHeight="1"/>
+    <row r="85" ht="45" customHeight="1"/>
+    <row r="86" ht="30" customHeight="1"/>
+    <row r="87" ht="60" customHeight="1"/>
+    <row r="88" ht="45" customHeight="1"/>
+    <row r="89" ht="30" customHeight="1"/>
+    <row r="90" ht="90" customHeight="1"/>
+    <row r="91" ht="45" customHeight="1"/>
+    <row r="92" ht="30" customHeight="1"/>
+    <row r="93" ht="75" customHeight="1"/>
+    <row r="94" ht="120" customHeight="1"/>
+    <row r="95" ht="75" customHeight="1"/>
+    <row r="96" ht="90" customHeight="1"/>
+    <row r="97" ht="120" customHeight="1"/>
+    <row r="98" ht="120" customHeight="1"/>
+    <row r="99" ht="120" customHeight="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O47" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O69" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="154">
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="A59:A63"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="A76:A78"/>
-    <mergeCell ref="A79:A81"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="A85:A87"/>
-    <mergeCell ref="A88:A90"/>
-    <mergeCell ref="A91:A93"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="B59:B63"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="B88:B90"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="C49:C53"/>
-    <mergeCell ref="C54:C58"/>
-    <mergeCell ref="C59:C63"/>
-    <mergeCell ref="C64:C68"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="C82:C84"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="C91:C93"/>
-    <mergeCell ref="D49:D53"/>
-    <mergeCell ref="D54:D58"/>
-    <mergeCell ref="D59:D63"/>
-    <mergeCell ref="D64:D68"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="D82:D84"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="D88:D90"/>
-    <mergeCell ref="D91:D93"/>
-    <mergeCell ref="E49:E53"/>
-    <mergeCell ref="E54:E58"/>
-    <mergeCell ref="E59:E63"/>
-    <mergeCell ref="E64:E68"/>
-    <mergeCell ref="E69:E71"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="E79:E81"/>
-    <mergeCell ref="E82:E84"/>
-    <mergeCell ref="E85:E87"/>
-    <mergeCell ref="E88:E90"/>
-    <mergeCell ref="E91:E93"/>
-    <mergeCell ref="F49:F53"/>
-    <mergeCell ref="F54:F58"/>
-    <mergeCell ref="F59:F63"/>
-    <mergeCell ref="F64:F68"/>
-    <mergeCell ref="F69:F71"/>
-    <mergeCell ref="F76:F78"/>
-    <mergeCell ref="F79:F81"/>
-    <mergeCell ref="F82:F84"/>
-    <mergeCell ref="F85:F87"/>
-    <mergeCell ref="F88:F90"/>
-    <mergeCell ref="F91:F93"/>
-    <mergeCell ref="G49:G53"/>
-    <mergeCell ref="G54:G58"/>
-    <mergeCell ref="G59:G63"/>
-    <mergeCell ref="G64:G68"/>
-    <mergeCell ref="G69:G71"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="G79:G81"/>
-    <mergeCell ref="G82:G84"/>
-    <mergeCell ref="G85:G87"/>
-    <mergeCell ref="G88:G90"/>
-    <mergeCell ref="G91:G93"/>
-    <mergeCell ref="H49:H53"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="H59:H63"/>
-    <mergeCell ref="H64:H68"/>
-    <mergeCell ref="H69:H71"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="H79:H81"/>
-    <mergeCell ref="H82:H84"/>
-    <mergeCell ref="H85:H87"/>
-    <mergeCell ref="H88:H90"/>
-    <mergeCell ref="H91:H93"/>
-    <mergeCell ref="I49:I53"/>
-    <mergeCell ref="I54:I58"/>
-    <mergeCell ref="I59:I63"/>
-    <mergeCell ref="I64:I68"/>
-    <mergeCell ref="I69:I71"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="I79:I81"/>
-    <mergeCell ref="I82:I84"/>
-    <mergeCell ref="I85:I87"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="I91:I93"/>
-    <mergeCell ref="K49:K53"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="K59:K63"/>
-    <mergeCell ref="K64:K68"/>
-    <mergeCell ref="K69:K71"/>
-    <mergeCell ref="K76:K78"/>
-    <mergeCell ref="K79:K81"/>
-    <mergeCell ref="K82:K84"/>
-    <mergeCell ref="K85:K87"/>
-    <mergeCell ref="K88:K90"/>
-    <mergeCell ref="K91:K93"/>
-    <mergeCell ref="L49:L53"/>
-    <mergeCell ref="L54:L58"/>
-    <mergeCell ref="L59:L63"/>
-    <mergeCell ref="L64:L68"/>
-    <mergeCell ref="L69:L71"/>
-    <mergeCell ref="L76:L78"/>
-    <mergeCell ref="L79:L81"/>
-    <mergeCell ref="L82:L84"/>
-    <mergeCell ref="L85:L87"/>
-    <mergeCell ref="L88:L90"/>
-    <mergeCell ref="L91:L93"/>
-    <mergeCell ref="M49:M53"/>
-    <mergeCell ref="M54:M58"/>
-    <mergeCell ref="M59:M63"/>
-    <mergeCell ref="M64:M68"/>
-    <mergeCell ref="M69:M71"/>
-    <mergeCell ref="M76:M78"/>
-    <mergeCell ref="M79:M81"/>
-    <mergeCell ref="M82:M84"/>
-    <mergeCell ref="M85:M87"/>
-    <mergeCell ref="M88:M90"/>
-    <mergeCell ref="M91:M93"/>
-    <mergeCell ref="N49:N53"/>
-    <mergeCell ref="N54:N58"/>
-    <mergeCell ref="N59:N63"/>
-    <mergeCell ref="N64:N68"/>
-    <mergeCell ref="N69:N71"/>
-    <mergeCell ref="N76:N78"/>
-    <mergeCell ref="N79:N81"/>
-    <mergeCell ref="N82:N84"/>
-    <mergeCell ref="N85:N87"/>
-    <mergeCell ref="N88:N90"/>
-    <mergeCell ref="N91:N93"/>
-    <mergeCell ref="O49:O53"/>
-    <mergeCell ref="O54:O58"/>
-    <mergeCell ref="O59:O63"/>
-    <mergeCell ref="O64:O68"/>
-    <mergeCell ref="O69:O71"/>
-    <mergeCell ref="O76:O78"/>
-    <mergeCell ref="O79:O81"/>
-    <mergeCell ref="O82:O84"/>
-    <mergeCell ref="O85:O87"/>
-    <mergeCell ref="O88:O90"/>
-    <mergeCell ref="O91:O93"/>
-  </mergeCells>
   <conditionalFormatting sqref="M2:M399">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"PASS"</formula>
@@ -6407,8 +5783,8 @@
       <formula1>"Chưa chạy,PASS,FAIL"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.25" right="0.25" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
 </worksheet>
 </file>